--- a/www/download/IND.surplus_value.empe_ls.r.pc.rpO2.xlsx
+++ b/www/download/IND.surplus_value.empe_ls.r.pc.rpO2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-79.68</t>
+          <t>-0.796835038052413</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-80.48</t>
+          <t>-0.804788083870844</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-74.4</t>
+          <t>-0.743974839592073</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-75.41</t>
+          <t>-0.754125597689546</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-84.46</t>
+          <t>-0.844608212931484</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-87.59</t>
+          <t>-0.87593147216485</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-86.1</t>
+          <t>-0.86095584293614</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-88.21</t>
+          <t>-0.882118412505374</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-88.4</t>
+          <t>-0.884043903569856</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-84.26</t>
+          <t>-0.842606301970499</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-89.7</t>
+          <t>-0.897008454320744</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-90.34</t>
+          <t>-0.903441239954049</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-90.7</t>
+          <t>-0.906989168107692</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-89.51</t>
+          <t>-0.895054129979023</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-85.59</t>
+          <t>-0.855931028931936</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-77.87</t>
+          <t>-0.778665734183239</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-78.84</t>
+          <t>-0.788434712027963</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-68.63</t>
+          <t>-0.686322976152911</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-71.34</t>
+          <t>-0.71338521516369</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-77.72</t>
+          <t>-0.777170112945342</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-83.06</t>
+          <t>-0.830600512796075</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-84.49</t>
+          <t>-0.844859176672647</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-84.33</t>
+          <t>-0.843328221441289</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-87.92</t>
+          <t>-0.879189246107164</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-84.3</t>
+          <t>-0.843044799768012</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-86.77</t>
+          <t>-0.867659961300289</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-87.98</t>
+          <t>-0.879804453539149</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-84.28</t>
+          <t>-0.842812601993127</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-81.82</t>
+          <t>-0.818172902540755</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-73.97</t>
+          <t>-0.73967141212489</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-78.84</t>
+          <t>-0.788430714177001</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-75.7</t>
+          <t>-0.756954618219614</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-68.8</t>
+          <t>-0.687977726391873</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-70.4</t>
+          <t>-0.704022115952161</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-76.57</t>
+          <t>-0.765667467466919</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-83.36</t>
+          <t>-0.833587524507574</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-84.11</t>
+          <t>-0.84106885004181</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-85.83</t>
+          <t>-0.858275770773434</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-89.11</t>
+          <t>-0.891055848331974</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-87.32</t>
+          <t>-0.873176125269277</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-89.44</t>
+          <t>-0.894419328004336</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-88.72</t>
+          <t>-0.88722582245579</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-85.66</t>
+          <t>-0.856595485539716</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-85.76</t>
+          <t>-0.857595446299328</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-81.19</t>
+          <t>-0.811850720134115</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>43.81</t>
+          <t>0.438109969583534</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>0.699005482467523</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>147.24</t>
+          <t>1.47240937406035</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>81.59</t>
+          <t>0.815900241407095</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>0.537995496339463</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.12</t>
+          <t>0.301197027502563</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>0.133271494878156</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.0173193061290233</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-31.22</t>
+          <t>-0.312226999983528</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-27.85</t>
+          <t>-0.278455720328336</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-33.45</t>
+          <t>-0.334541808424916</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-42.74</t>
+          <t>-0.427425998876446</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-37.31</t>
+          <t>-0.373134983660984</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>-29.27</t>
+          <t>-0.29267187630411</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>-17.03</t>
+          <t>-0.170321017938066</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>310.28</t>
+          <t>3.10276419428286</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>305.98</t>
+          <t>3.05984864656625</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>337.85</t>
+          <t>3.37848316424403</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>316.99</t>
+          <t>3.1699152309612</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>324.8</t>
+          <t>3.24795155558527</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>181.42</t>
+          <t>1.81423497524515</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>170.38</t>
+          <t>1.70381717045332</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>206.63</t>
+          <t>2.06633802582195</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>193.37</t>
+          <t>1.93370302419645</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>158.13</t>
+          <t>1.58129823284713</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>1.3370471983447</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>118.39</t>
+          <t>1.18385145893344</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>128.39</t>
+          <t>1.28391412320938</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>114.11</t>
+          <t>1.14105299474865</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>184.42</t>
+          <t>1.84424456014149</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-54.97</t>
+          <t>-0.549706407095358</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-54.44</t>
+          <t>-0.544366440533593</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-50.14</t>
+          <t>-0.501370055440888</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-56.72</t>
+          <t>-0.567181548972478</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-65.04</t>
+          <t>-0.650420445507153</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-78.39</t>
+          <t>-0.783929916409955</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-80.1</t>
+          <t>-0.800990692639932</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-76.94</t>
+          <t>-0.769366234256798</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-78.42</t>
+          <t>-0.784186625424395</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-77.76</t>
+          <t>-0.777646048784169</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-82.54</t>
+          <t>-0.825410338827459</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>-81.66</t>
+          <t>-0.816630890165848</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>-77.32</t>
+          <t>-0.773208323080729</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>-75.13</t>
+          <t>-0.751273602797363</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>-65.79</t>
+          <t>-0.657890735244573</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-25.82</t>
+          <t>-0.258214721689341</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-23.62</t>
+          <t>-0.236160885133867</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-18.71</t>
+          <t>-0.187079540510525</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-14.72</t>
+          <t>-0.147232777091816</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-11.66</t>
+          <t>-0.11659308545379</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-12.4</t>
+          <t>-0.123970025839564</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-0.0493786252353381</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.0125217108077369</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>0.0590843613877097</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>0.0702146456462476</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>0.100704708039683</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>13.62</t>
+          <t>0.136157966193666</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>28.22</t>
+          <t>0.28217760831123</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>0.29076179440678</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>39.97</t>
+          <t>0.399743998101965</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-48.65</t>
+          <t>-0.486477971249907</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-56.7</t>
+          <t>-0.567025230179115</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-30.03</t>
+          <t>-0.30034059224095</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-42.85</t>
+          <t>-0.428477334159746</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-64.02</t>
+          <t>-0.640167505574693</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-71.91</t>
+          <t>-0.719070466554254</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-75.09</t>
+          <t>-0.750861581653007</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-76.22</t>
+          <t>-0.762198446652785</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-79.4</t>
+          <t>-0.793962182108438</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-73.66</t>
+          <t>-0.736560041555311</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-67.17</t>
+          <t>-0.671658364044385</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>-61.37</t>
+          <t>-0.613731475464008</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>-56.17</t>
+          <t>-0.561743743949434</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>-50.42</t>
+          <t>-0.504219885765909</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-0.0611030055730177</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>0.356661752399119</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-22.44</t>
+          <t>-0.22443716787567</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>15.37</t>
+          <t>0.153659345156357</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-0.0452759941898783</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-25.42</t>
+          <t>-0.254182325663</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-44.69</t>
+          <t>-0.446912449820374</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-58.67</t>
+          <t>-0.586741114286742</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-62.96</t>
+          <t>-0.629602480261722</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-77.1</t>
+          <t>-0.771040731259393</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-66.42</t>
+          <t>-0.664244071972574</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-71.93</t>
+          <t>-0.719323424708236</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>-72.2</t>
+          <t>-0.721983768456559</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>-67.71</t>
+          <t>-0.677129857915515</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>-65.21</t>
+          <t>-0.652051157664959</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>-40.63</t>
+          <t>-0.406321424284522</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-80.93</t>
+          <t>-0.809307605106282</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-78.3</t>
+          <t>-0.783000068389347</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-74.31</t>
+          <t>-0.74305271033192</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-76.81</t>
+          <t>-0.76812713885407</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-82.54</t>
+          <t>-0.825376661592141</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-87.59</t>
+          <t>-0.875850428754792</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-89.07</t>
+          <t>-0.89067175344647</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-89.24</t>
+          <t>-0.892371102839551</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-90.01</t>
+          <t>-0.900050822374948</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-88.64</t>
+          <t>-0.886378821104939</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-89.82</t>
+          <t>-0.898232959158455</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>-90.36</t>
+          <t>-0.90358915152489</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>-87.98</t>
+          <t>-0.879798067757198</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>-86.27</t>
+          <t>-0.86265622643718</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>-80.22</t>
+          <t>-0.802192512852343</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-89.8</t>
+          <t>-0.897975012760272</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-89.22</t>
+          <t>-0.892247658493</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-84.54</t>
+          <t>-0.845357223519891</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-85.38</t>
+          <t>-0.853835260570586</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-87.01</t>
+          <t>-0.870070222660342</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-88.78</t>
+          <t>-0.887800331080555</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-89.65</t>
+          <t>-0.896464589150066</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-90.35</t>
+          <t>-0.903521865340971</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-90.92</t>
+          <t>-0.909230971135061</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-91.01</t>
+          <t>-0.910125904753476</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-92.06</t>
+          <t>-0.920564094213654</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>-91.56</t>
+          <t>-0.915628821844194</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>-90.72</t>
+          <t>-0.90722741315499</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>-91.47</t>
+          <t>-0.914651644320514</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>-85.71</t>
+          <t>-0.857118030682611</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-67.65</t>
+          <t>-0.67648103311279</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-68.27</t>
+          <t>-0.682731069162951</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>-62.3</t>
+          <t>-0.623005072373264</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-65.36</t>
+          <t>-0.653609033079094</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-75.08</t>
+          <t>-0.750766771998117</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-83.5</t>
+          <t>-0.834959839336646</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-84.24</t>
+          <t>-0.84244558665585</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-83.68</t>
+          <t>-0.836784791263966</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-86.73</t>
+          <t>-0.867327895060654</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-85.89</t>
+          <t>-0.858886883277171</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-88.07</t>
+          <t>-0.880727271174786</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>-88.79</t>
+          <t>-0.887923156070823</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>-86.61</t>
+          <t>-0.866069250819758</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>-85.62</t>
+          <t>-0.8561883730974</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>-78.18</t>
+          <t>-0.781831117543926</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>448.56</t>
+          <t>4.4856092571416</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>407.63</t>
+          <t>4.07632402824238</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>653.59</t>
+          <t>6.53585314658713</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>597.05</t>
+          <t>5.97050019928407</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>0.0780447608308259</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-63.9</t>
+          <t>-0.639035692554335</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-65.81</t>
+          <t>-0.658087578925945</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-74.37</t>
+          <t>-0.743684710734613</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-88.36</t>
+          <t>-0.883577931080847</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-74.45</t>
+          <t>-0.744539132935243</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-59.73</t>
+          <t>-0.597332736742973</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>-73</t>
+          <t>-0.730031038977064</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>-80.09</t>
+          <t>-0.800919821430727</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>-82.16</t>
+          <t>-0.821576760566995</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>-73.69</t>
+          <t>-0.736868380402818</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-76.96</t>
+          <t>-0.769609250587728</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-77.48</t>
+          <t>-0.774816107910135</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-68</t>
+          <t>-0.679972110415763</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-70.81</t>
+          <t>-0.708064097328478</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-77.89</t>
+          <t>-0.778884745388684</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-81.32</t>
+          <t>-0.813167239299533</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-83.85</t>
+          <t>-0.838461799966485</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-84.1</t>
+          <t>-0.841029865980542</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-88.64</t>
+          <t>-0.88642521112914</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-88.04</t>
+          <t>-0.880423104078713</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-88.67</t>
+          <t>-0.886669721376249</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>-89.01</t>
+          <t>-0.890130991876667</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>-86.89</t>
+          <t>-0.868945559443587</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>-86.74</t>
+          <t>-0.867396319587307</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>-80.04</t>
+          <t>-0.800401707440678</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-85.49</t>
+          <t>-0.854894224721956</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-84.14</t>
+          <t>-0.841425779640655</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-80.77</t>
+          <t>-0.80768764151372</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-81.67</t>
+          <t>-0.81668292908473</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-86.29</t>
+          <t>-0.862947611037909</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-90.32</t>
+          <t>-0.903179761866652</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-90.93</t>
+          <t>-0.909332602881247</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-91.52</t>
+          <t>-0.915243225405086</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-93.84</t>
+          <t>-0.938369899941757</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-93</t>
+          <t>-0.929953551718072</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>-94.24</t>
+          <t>-0.942440604052235</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-94.3</t>
+          <t>-0.943015402217235</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>-92.9</t>
+          <t>-0.928969766101885</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>-92.47</t>
+          <t>-0.92471382721384</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>-88.87</t>
+          <t>-0.888745975938539</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-84.02</t>
+          <t>-0.840238073148169</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-83.13</t>
+          <t>-0.831309123871969</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>-76.62</t>
+          <t>-0.766207190960273</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-77.85</t>
+          <t>-0.778535926990447</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-83.48</t>
+          <t>-0.834784854131687</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-87.63</t>
+          <t>-0.876349253373461</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-88.87</t>
+          <t>-0.888746190083695</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-88.99</t>
+          <t>-0.889874453440645</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-90.06</t>
+          <t>-0.900629198119151</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-90.39</t>
+          <t>-0.903889064169139</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>-91.6</t>
+          <t>-0.915998314420051</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>-92.08</t>
+          <t>-0.920775880811871</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>-91.2</t>
+          <t>-0.912047417797071</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>-90.21</t>
+          <t>-0.902054512997591</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>-87.03</t>
+          <t>-0.870280809548134</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-38.37</t>
+          <t>-0.383692621254965</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-42.47</t>
+          <t>-0.424657898392081</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>-21.27</t>
+          <t>-0.212652039345328</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-27.97</t>
+          <t>-0.279718253630456</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-45.97</t>
+          <t>-0.459667291105192</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-68.63</t>
+          <t>-0.686297961274851</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-73.2</t>
+          <t>-0.732014067518491</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-75.53</t>
+          <t>-0.755283302780273</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>-82.02</t>
+          <t>-0.820202696323598</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-76.81</t>
+          <t>-0.768099304107914</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>-83.82</t>
+          <t>-0.838235694187167</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>-86.72</t>
+          <t>-0.867154955885105</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>-83.93</t>
+          <t>-0.839263201802019</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>-83.55</t>
+          <t>-0.835543198192638</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>-76.2</t>
+          <t>-0.76201515612035</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-11.26</t>
+          <t>-0.112602079263157</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.00832860481935715</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>34.47</t>
+          <t>0.344674944632447</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>0.0522871591921596</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-19.89</t>
+          <t>-0.198901066967323</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-28.32</t>
+          <t>-0.283180996777218</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-45.01</t>
+          <t>-0.450077164053802</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-44.69</t>
+          <t>-0.446892657830399</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>-71.31</t>
+          <t>-0.71308485072587</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-53.68</t>
+          <t>-0.536752131626884</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>-56.09</t>
+          <t>-0.560897227346351</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>-52.59</t>
+          <t>-0.525898384287522</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>-49.41</t>
+          <t>-0.494141485880652</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>-25.71</t>
+          <t>-0.257126602068217</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>0.327543987727148</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>284.68</t>
+          <t>2.84678869616152</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>267.56</t>
+          <t>2.67555700300037</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>298.82</t>
+          <t>2.98815246534198</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>338.15</t>
+          <t>3.38154045238393</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>195.44</t>
+          <t>1.95438675602945</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>0.939404618514731</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>0.828964711360008</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.87</t>
+          <t>0.76871131381224</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>58.89</t>
+          <t>0.588862810691643</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>59.07</t>
+          <t>0.590695565189235</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>46.23</t>
+          <t>0.462305555503186</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>39.34</t>
+          <t>0.393396520769552</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>60.29</t>
+          <t>0.602905741145204</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>52.79</t>
+          <t>0.527867192604628</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>95.97</t>
+          <t>0.959745729714659</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>220.65</t>
+          <t>2.20647165034806</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>243.95</t>
+          <t>2.43947341709371</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>233.38</t>
+          <t>2.33381939766075</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>233.46</t>
+          <t>2.33464816948511</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>195.02</t>
+          <t>1.95018995825513</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>191.48</t>
+          <t>1.91481860486395</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>208.78</t>
+          <t>2.08779005409256</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>227.63</t>
+          <t>2.27629144524022</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>247.22</t>
+          <t>2.47220932654357</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>255.02</t>
+          <t>2.55022728490379</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>252.32</t>
+          <t>2.52323412122642</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>256.04</t>
+          <t>2.56043320188966</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>268.95</t>
+          <t>2.6895324332725</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>293.63</t>
+          <t>2.93626047361766</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>309.54</t>
+          <t>3.09536222084222</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-70.49</t>
+          <t>-0.704872271186603</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-66.16</t>
+          <t>-0.661558028879326</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-72</t>
+          <t>-0.719981437904439</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-72.42</t>
+          <t>-0.724153030051276</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-75.49</t>
+          <t>-0.754872181097043</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-80.25</t>
+          <t>-0.802491454177952</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-79.86</t>
+          <t>-0.798586066708271</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-80.54</t>
+          <t>-0.805377746342549</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-84.03</t>
+          <t>-0.84025413654954</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-86.55</t>
+          <t>-0.865452909281855</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-89.9</t>
+          <t>-0.899043512209486</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-89.62</t>
+          <t>-0.896200017747951</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-89.44</t>
+          <t>-0.894443175664205</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-87.71</t>
+          <t>-0.877112393129044</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-86.48</t>
+          <t>-0.864815169018912</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-68.59</t>
+          <t>-0.685917452409643</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-67.78</t>
+          <t>-0.67784624422983</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-60.58</t>
+          <t>-0.605811920164923</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-59.69</t>
+          <t>-0.596924308782325</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-69.71</t>
+          <t>-0.697081559193293</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-78.12</t>
+          <t>-0.781206597298359</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-79.61</t>
+          <t>-0.796079960789777</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-79.9</t>
+          <t>-0.799035358112572</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-82.6</t>
+          <t>-0.825993329811548</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-81.57</t>
+          <t>-0.815711199875689</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-84.74</t>
+          <t>-0.847419653630702</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-86.38</t>
+          <t>-0.86379624970755</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-83.73</t>
+          <t>-0.837347757499307</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-84.16</t>
+          <t>-0.8416401784763</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-77.56</t>
+          <t>-0.775615555846403</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-66.71</t>
+          <t>-0.667057748742847</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-66.55</t>
+          <t>-0.665485379396267</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>-58.75</t>
+          <t>-0.587524097561104</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-54.5</t>
+          <t>-0.544968397341597</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-69.49</t>
+          <t>-0.694875227697985</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.91</t>
+          <t>-0.769085287153586</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-77.91</t>
+          <t>-0.77908620630949</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-77.98</t>
+          <t>-0.779768394472965</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>-80.61</t>
+          <t>-0.806117487516617</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-81.11</t>
+          <t>-0.811114561090194</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>-83.39</t>
+          <t>-0.833928824884349</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>-83.2</t>
+          <t>-0.832008799383953</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>-78.79</t>
+          <t>-0.787946939574933</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>-80.23</t>
+          <t>-0.802303439015007</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>-72.51</t>
+          <t>-0.725098134877892</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-59</t>
+          <t>-0.589993368614098</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-58.74</t>
+          <t>-0.58738259262452</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-56.07</t>
+          <t>-0.560711106159568</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-45.06</t>
+          <t>-0.450641920869863</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-64.27</t>
+          <t>-0.642671177470921</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.58</t>
+          <t>-0.775807476520011</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-76.05</t>
+          <t>-0.760519495866193</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-71.69</t>
+          <t>-0.716918107623487</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>-74.3</t>
+          <t>-0.742989952619496</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-72.36</t>
+          <t>-0.723623748710204</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>-77.39</t>
+          <t>-0.773895764731147</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>-78.64</t>
+          <t>-0.786350728798745</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>-74.03</t>
+          <t>-0.740263945798077</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>-73.66</t>
+          <t>-0.736620089492743</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>-61.79</t>
+          <t>-0.617947959292049</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-21.95</t>
+          <t>-0.219489178252909</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-44.54</t>
+          <t>-0.445434412658957</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>-47.58</t>
+          <t>-0.475755011498359</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-39.11</t>
+          <t>-0.391060393610745</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-46.3</t>
+          <t>-0.463020367950769</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-51.88</t>
+          <t>-0.518778324426336</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-69.22</t>
+          <t>-0.69218128748428</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-62.61</t>
+          <t>-0.626102022071087</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>-75.19</t>
+          <t>-0.751856595640177</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-76.48</t>
+          <t>-0.764811149679754</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>-80.14</t>
+          <t>-0.801425546594815</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>-80.24</t>
+          <t>-0.802405211663523</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>-88.23</t>
+          <t>-0.882342778351297</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>-85.83</t>
+          <t>-0.858296938554622</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>-69.25</t>
+          <t>-0.692493594482657</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-74.34</t>
+          <t>-0.743433549944837</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-82.85</t>
+          <t>-0.828482898327694</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>-80.47</t>
+          <t>-0.804741465827506</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-81.38</t>
+          <t>-0.813828189817248</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-84.79</t>
+          <t>-0.847934377986587</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-88.98</t>
+          <t>-0.889771548266479</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-89.32</t>
+          <t>-0.893208472997709</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-87.91</t>
+          <t>-0.879078672160822</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>-92.05</t>
+          <t>-0.920457486387393</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-88.96</t>
+          <t>-0.889646754736398</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>-91.15</t>
+          <t>-0.91147336283669</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>-91.18</t>
+          <t>-0.911764951437599</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>-89.33</t>
+          <t>-0.893295087965072</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>-88.09</t>
+          <t>-0.880906147950531</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>-85.51</t>
+          <t>-0.855085121012677</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>0.411045903705913</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>25.29</t>
+          <t>0.252934786878314</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>39.51</t>
+          <t>0.395103226889044</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>11.97</t>
+          <t>0.119697655601924</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-6.31</t>
+          <t>-0.0631497125098642</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-17.54</t>
+          <t>-0.17535736460221</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-43.16</t>
+          <t>-0.431630615592594</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-35.92</t>
+          <t>-0.35918606126143</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>-42.85</t>
+          <t>-0.42849291557426</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>0.846035863237529</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>749.41</t>
+          <t>7.49410285934108</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>234.73</t>
+          <t>2.34730660404343</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>-68.69</t>
+          <t>-0.686883006043064</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>-66.94</t>
+          <t>-0.669383987682317</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>-48.05</t>
+          <t>-0.480454079533169</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>506.48</t>
+          <t>5.0648252648318</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>537.43</t>
+          <t>5.37425909018927</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>571.77</t>
+          <t>5.71770256061736</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>457.51</t>
+          <t>4.57510186146103</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>339.93</t>
+          <t>3.39933798574948</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>218.93</t>
+          <t>2.18930087229319</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>156.87</t>
+          <t>1.56869371959493</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>157.04</t>
+          <t>1.57041602958075</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>183.04</t>
+          <t>1.83036563601172</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>209.95</t>
+          <t>2.09946318114923</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>170.53</t>
+          <t>1.70534188152052</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>180.23</t>
+          <t>1.80230998518904</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>226.76</t>
+          <t>2.26761645508073</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>303.3</t>
+          <t>3.03302074308436</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>474.49</t>
+          <t>4.74489263140523</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>61.28</t>
+          <t>0.612753675980358</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>35.77</t>
+          <t>0.357662233849417</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>195.98</t>
+          <t>1.95978314054804</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>74.83</t>
+          <t>0.748269831001178</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>18.32</t>
+          <t>0.183153618574388</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.0209179692931829</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-44.97</t>
+          <t>-0.44970835588207</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-41.51</t>
+          <t>-0.415142521319904</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>-53.69</t>
+          <t>-0.536927793744111</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-33.2</t>
+          <t>-0.332038675329906</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>-26.93</t>
+          <t>-0.269330205548013</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>-33.26</t>
+          <t>-0.332649582184596</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>-0.132623031097158</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.0145436104728449</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>41.11</t>
+          <t>0.411057245817918</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-90.88</t>
+          <t>-0.908819340229937</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-90.84</t>
+          <t>-0.908431517531972</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-85.73</t>
+          <t>-0.857334057155911</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-88.84</t>
+          <t>-0.888357925143034</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-90.58</t>
+          <t>-0.905825090896679</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-92.43</t>
+          <t>-0.924344334097228</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-92.42</t>
+          <t>-0.924229232040406</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-92.02</t>
+          <t>-0.920208549386954</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-94.23</t>
+          <t>-0.942318649555312</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-93.05</t>
+          <t>-0.930483975608469</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-93.92</t>
+          <t>-0.939151219388512</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-93.84</t>
+          <t>-0.938358536103525</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-93.03</t>
+          <t>-0.93029441591151</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-92.72</t>
+          <t>-0.927153884183429</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-90.58</t>
+          <t>-0.905766750861563</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>0.0609880331528274</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-0.0594361025057426</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>0.12409005166939</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-14.04</t>
+          <t>-0.140443055570731</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-21.82</t>
+          <t>-0.218203567010599</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-36.57</t>
+          <t>-0.365660500922984</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-20.26</t>
+          <t>-0.202646739187441</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-15.6</t>
+          <t>-0.156033443354238</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>-41.15</t>
+          <t>-0.4115163875513</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-18.88</t>
+          <t>-0.188775102130418</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>-23.06</t>
+          <t>-0.230640059859658</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>-25.43</t>
+          <t>-0.254342724923429</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>-23.44</t>
+          <t>-0.234399337499636</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>-28.49</t>
+          <t>-0.284894961824228</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>-0.111058306266389</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>-49.05</t>
+          <t>-0.49050170003419</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-49.92</t>
+          <t>-0.499246025624321</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>-35.57</t>
+          <t>-0.35568234601413</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-43.62</t>
+          <t>-0.43621054396816</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-57.44</t>
+          <t>-0.574389836639892</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-72.9</t>
+          <t>-0.72897299405314</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-73.77</t>
+          <t>-0.737686025103686</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-73.17</t>
+          <t>-0.731727332475198</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>-79.54</t>
+          <t>-0.795389880838934</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-77.75</t>
+          <t>-0.777464488924939</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>-82.52</t>
+          <t>-0.825235766179787</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>-83.51</t>
+          <t>-0.835076116628764</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>-82.2</t>
+          <t>-0.822006932603759</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>-83.1</t>
+          <t>-0.831012380773779</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>-70.92</t>
+          <t>-0.7091992202968</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>126.94</t>
+          <t>1.26940095482922</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>123.42</t>
+          <t>1.23420544150047</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>176.46</t>
+          <t>1.76464489191381</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>102.94</t>
+          <t>1.02939199307583</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>139.87</t>
+          <t>1.39872706830511</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>65.25</t>
+          <t>0.65246233531707</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>37.68</t>
+          <t>0.376847038326648</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>35.14</t>
+          <t>0.351394638045139</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.0106871769953019</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>62.08</t>
+          <t>0.620834693118453</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>0.0655879275506657</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-0.040909256568877</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>-57.21</t>
+          <t>-0.572098872244969</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>-62.91</t>
+          <t>-0.629077250867961</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>-32.44</t>
+          <t>-0.324394305880985</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>206.99</t>
+          <t>2.0698549564749</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>159.49</t>
+          <t>1.59491277168362</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>205.05</t>
+          <t>2.05048860091048</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>201.08</t>
+          <t>2.01080175830764</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>222.06</t>
+          <t>2.22061522523582</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>126.71</t>
+          <t>1.26712237176937</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>118.36</t>
+          <t>1.1835692615489</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>99.81</t>
+          <t>0.998108957005499</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>78.02</t>
+          <t>0.780224096152813</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>100.02</t>
+          <t>1.00023969605204</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>86.56</t>
+          <t>0.865561916221575</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>74.59</t>
+          <t>0.745917895665408</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>66.08</t>
+          <t>0.66082940799089</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>52.34</t>
+          <t>0.523357497127162</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>0.972012129080452</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>0.463193182331193</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>50.44</t>
+          <t>0.504360716200465</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>0.564035447712064</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>0.170510948579635</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>0.118000877199069</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-22.02</t>
+          <t>-0.220244467115554</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-32.14</t>
+          <t>-0.321355281012312</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-34.39</t>
+          <t>-0.343886050010362</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>-66.98</t>
+          <t>-0.669800695512269</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-63.28</t>
+          <t>-0.632792523300245</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>-66.05</t>
+          <t>-0.6605063843547</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>-65.47</t>
+          <t>-0.654697121498268</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>-69.43</t>
+          <t>-0.694324294949721</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>-67.53</t>
+          <t>-0.675276549660081</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>-64.57</t>
+          <t>-0.645707663655431</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-80.57</t>
+          <t>-0.805699094194232</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-79.75</t>
+          <t>-0.797477210183349</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>-73.49</t>
+          <t>-0.734876470063957</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-74.15</t>
+          <t>-0.741541732997323</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-80.19</t>
+          <t>-0.801887383820069</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-84.95</t>
+          <t>-0.849515202707817</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-85.6</t>
+          <t>-0.855959576254555</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-86.07</t>
+          <t>-0.860691081941021</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>-87.96</t>
+          <t>-0.879588281264913</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-88.27</t>
+          <t>-0.882681387617542</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>-89.57</t>
+          <t>-0.895666171243985</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>-89.78</t>
+          <t>-0.897836069723293</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>-88.82</t>
+          <t>-0.888160117852918</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>-91.01</t>
+          <t>-0.910053028823796</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>-86.9</t>
+          <t>-0.868966802387366</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-88.35</t>
+          <t>-0.88352348040416</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-88.2</t>
+          <t>-0.882044581376691</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>-85.13</t>
+          <t>-0.851326857471217</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-86.45</t>
+          <t>-0.864510384360088</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-89.11</t>
+          <t>-0.891064911394907</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-92.13</t>
+          <t>-0.921289940655926</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-92.49</t>
+          <t>-0.924924688525791</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-92.24</t>
+          <t>-0.922366710312112</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>-94.11</t>
+          <t>-0.941076407331986</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-93.59</t>
+          <t>-0.935910880074954</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>-94.3</t>
+          <t>-0.943048554581736</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>-93.81</t>
+          <t>-0.938106920077908</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>-93.47</t>
+          <t>-0.934668632350922</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>-92.17</t>
+          <t>-0.921739339297629</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>-89.21</t>
+          <t>-0.892104544890782</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>70.03</t>
+          <t>0.70029064481268</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>0.485633287378827</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>0.202896363210695</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>14.22</t>
+          <t>0.142217626617338</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-13.39</t>
+          <t>-0.133915133622113</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-27.41</t>
+          <t>-0.274106285878701</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>0.0762974292120024</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>86.14</t>
+          <t>0.861384707923056</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>86.53</t>
+          <t>0.865288707004946</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>98.87</t>
+          <t>0.98874717160869</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>78.53</t>
+          <t>0.785310956262333</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>0.903287058028709</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>111.9</t>
+          <t>1.11895483955355</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>108.89</t>
+          <t>1.08887801429404</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>264.51</t>
+          <t>2.6451283333743</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>-73.44</t>
+          <t>-0.734391827678723</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-74.78</t>
+          <t>-0.747842966969444</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>-69.81</t>
+          <t>-0.698122957565003</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-71.04</t>
+          <t>-0.710386876556299</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-79.05</t>
+          <t>-0.790478248615635</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-85.05</t>
+          <t>-0.850460146266499</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-84.65</t>
+          <t>-0.846482190617826</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-86.12</t>
+          <t>-0.861241098126767</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>-86.18</t>
+          <t>-0.861838409706148</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-84.73</t>
+          <t>-0.84733746762008</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>-85.28</t>
+          <t>-0.85280957036099</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>-83.85</t>
+          <t>-0.838490871959574</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>-77.82</t>
+          <t>-0.778151710000684</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>-76.43</t>
+          <t>-0.764307251605391</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>-63.56</t>
+          <t>-0.635623833752538</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>-66.85</t>
+          <t>-0.66853311423116</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-63.88</t>
+          <t>-0.638761471959349</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>-62.79</t>
+          <t>-0.627894808853549</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-62.89</t>
+          <t>-0.628856037000757</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-66.72</t>
+          <t>-0.667223122770239</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-78.15</t>
+          <t>-0.781517490488591</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-78.05</t>
+          <t>-0.780538970268436</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-76.05</t>
+          <t>-0.760488556332634</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>-75.99</t>
+          <t>-0.759857714259277</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-78.61</t>
+          <t>-0.786139537848836</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>-81.13</t>
+          <t>-0.811334877047255</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>-80.44</t>
+          <t>-0.804448891225414</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>-78.35</t>
+          <t>-0.783494143052617</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>-76.98</t>
+          <t>-0.769838003667943</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>-65.64</t>
+          <t>-0.656445363065275</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>905.77</t>
+          <t>9.05771241126758</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>864.42</t>
+          <t>8.64422747757096</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>798.1</t>
+          <t>7.98095259558822</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>854.48</t>
+          <t>8.54475299386076</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>891.04</t>
+          <t>8.91042401300222</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>840.68</t>
+          <t>8.4067828997058</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>839.75</t>
+          <t>8.3974716620204</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>846.23</t>
+          <t>8.46226810545338</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>756.71</t>
+          <t>7.56713164799192</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>834.59</t>
+          <t>8.34591133789337</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>839.28</t>
+          <t>8.39284988951318</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>822.15</t>
+          <t>8.22151680937497</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>845.63</t>
+          <t>8.45633665929867</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>752.71</t>
+          <t>7.52713474430096</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>742.1</t>
+          <t>7.42095476863219</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>434.05</t>
+          <t>4.34046870323123</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>410.58</t>
+          <t>4.10583175264832</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>427.51</t>
+          <t>4.27510728028707</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>469.6</t>
+          <t>4.69599052429619</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>487.61</t>
+          <t>4.87610950703708</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>456.2</t>
+          <t>4.561985176098</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>450.38</t>
+          <t>4.5038317316371</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>439.8</t>
+          <t>4.39803477898332</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>401.32</t>
+          <t>4.01317618391131</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>398.61</t>
+          <t>3.98609824411397</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>384.85</t>
+          <t>3.84850447421551</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>371.92</t>
+          <t>3.71923695433918</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>372.97</t>
+          <t>3.72966169016464</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>337.57</t>
+          <t>3.37572348996221</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>351.62</t>
+          <t>3.51622351769277</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
